--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_24.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_22_24.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>243053.5986293328</v>
+        <v>239065.6970920833</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8041530.902064408</v>
+        <v>8041589.773721423</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17785268.30061069</v>
+        <v>17785260.94054101</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5950202.376106265</v>
+        <v>5950093.158386756</v>
       </c>
     </row>
     <row r="11">
@@ -8667,31 +8667,31 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K11" t="n">
-        <v>135.713494261061</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L11" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M11" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N11" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O11" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P11" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q11" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R11" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -8746,28 +8746,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J12" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K12" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L12" t="n">
-        <v>61.49470996855341</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M12" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N12" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O12" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P12" t="n">
-        <v>66.2029923199906</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q12" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8825,25 +8825,25 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K13" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L13" t="n">
-        <v>90.64844677304154</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M13" t="n">
-        <v>92.28488230826079</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N13" t="n">
-        <v>82.15365921933152</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O13" t="n">
-        <v>96.40047287807228</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P13" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q13" t="n">
         <v>65.34295837775146</v>
@@ -8904,31 +8904,31 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K14" t="n">
-        <v>135.713494261061</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L14" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M14" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N14" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O14" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P14" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q14" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R14" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -8983,28 +8983,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J15" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K15" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L15" t="n">
-        <v>61.49470996855341</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M15" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N15" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O15" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P15" t="n">
-        <v>66.2029923199906</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9062,25 +9062,25 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K16" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L16" t="n">
-        <v>90.64844677304154</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M16" t="n">
-        <v>92.28488230826079</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N16" t="n">
-        <v>82.15365921933152</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O16" t="n">
-        <v>96.40047287807228</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P16" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q16" t="n">
         <v>65.34295837775146</v>
@@ -9141,31 +9141,31 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K17" t="n">
-        <v>135.713494261061</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L17" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M17" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N17" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O17" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P17" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q17" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R17" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -9220,28 +9220,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J18" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K18" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L18" t="n">
-        <v>61.49470996855341</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M18" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N18" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O18" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P18" t="n">
-        <v>66.2029923199906</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9299,25 +9299,25 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K19" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L19" t="n">
-        <v>90.64844677304154</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M19" t="n">
-        <v>92.28488230826079</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N19" t="n">
-        <v>82.15365921933152</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O19" t="n">
-        <v>96.40047287807228</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P19" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q19" t="n">
         <v>65.34295837775146</v>
@@ -9378,31 +9378,31 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>124.7477386975405</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K20" t="n">
-        <v>135.713494261061</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L20" t="n">
-        <v>131.0900833116958</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M20" t="n">
-        <v>113.8736452875743</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N20" t="n">
-        <v>111.0558274156864</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O20" t="n">
-        <v>118.336829512139</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P20" t="n">
-        <v>135.8472419864253</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q20" t="n">
-        <v>150.6749612312334</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R20" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -9457,28 +9457,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J21" t="n">
-        <v>93.30682477987423</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K21" t="n">
-        <v>80.5319578422835</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L21" t="n">
-        <v>61.49470996855341</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M21" t="n">
-        <v>52.20903392201832</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N21" t="n">
-        <v>39.03666491352197</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O21" t="n">
-        <v>58.15515953878405</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P21" t="n">
-        <v>66.2029923199906</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.6783778596064</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9536,25 +9536,25 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K22" t="n">
-        <v>94.444405711519</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L22" t="n">
-        <v>90.64844677304154</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M22" t="n">
-        <v>92.28488230826079</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N22" t="n">
-        <v>82.15365921933152</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O22" t="n">
-        <v>96.40047287807228</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P22" t="n">
-        <v>101.7417745409509</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q22" t="n">
         <v>65.34295837775146</v>
@@ -9615,31 +9615,31 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K23" t="n">
-        <v>135.2021224017645</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L23" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M23" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N23" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O23" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P23" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q23" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R23" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -9694,28 +9694,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J24" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K24" t="n">
-        <v>80.18462765360428</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L24" t="n">
-        <v>61.02768166666662</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M24" t="n">
-        <v>51.66403392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N24" t="n">
-        <v>38.4772403852201</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O24" t="n">
-        <v>57.64339538784067</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P24" t="n">
-        <v>65.79225647093401</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q24" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9773,25 +9773,25 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K25" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L25" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M25" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N25" t="n">
-        <v>81.8777083996594</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O25" t="n">
-        <v>96.14558763217065</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P25" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q25" t="n">
         <v>65.34295837775146</v>
@@ -9852,28 +9852,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K26" t="n">
-        <v>135.2021224017644</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L26" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M26" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N26" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O26" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P26" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q26" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R26" t="n">
         <v>65.71641987298243</v>
@@ -9931,28 +9931,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J27" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K27" t="n">
-        <v>80.18462765360425</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L27" t="n">
-        <v>61.02768166666661</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M27" t="n">
-        <v>51.66403392201831</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N27" t="n">
-        <v>38.47724038522007</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O27" t="n">
-        <v>57.64339538784064</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P27" t="n">
-        <v>65.79225647093399</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q27" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10013,22 +10013,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K28" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L28" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M28" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N28" t="n">
-        <v>81.87770839965938</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O28" t="n">
-        <v>96.14558763217063</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P28" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q28" t="n">
         <v>65.34295837775146</v>
@@ -10089,28 +10089,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K29" t="n">
-        <v>135.2021224017644</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L29" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M29" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N29" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O29" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P29" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q29" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R29" t="n">
         <v>65.71641987298243</v>
@@ -10168,28 +10168,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J30" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K30" t="n">
-        <v>80.18462765360425</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L30" t="n">
-        <v>61.02768166666661</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M30" t="n">
-        <v>51.66403392201831</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N30" t="n">
-        <v>38.47724038522007</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O30" t="n">
-        <v>57.64339538795637</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P30" t="n">
-        <v>65.79225647093399</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q30" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10250,22 +10250,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K31" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L31" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M31" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N31" t="n">
-        <v>81.87770839965938</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O31" t="n">
-        <v>96.14558763217063</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P31" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q31" t="n">
         <v>65.34295837775146</v>
@@ -10326,31 +10326,31 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K32" t="n">
-        <v>135.2021224017645</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L32" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M32" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N32" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O32" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P32" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q32" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R32" t="n">
-        <v>65.71641987298244</v>
+        <v>65.71641987298243</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -10405,28 +10405,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J33" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K33" t="n">
-        <v>80.18462765360428</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L33" t="n">
-        <v>61.02768166666662</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M33" t="n">
-        <v>51.66403392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N33" t="n">
-        <v>38.47724038532338</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O33" t="n">
-        <v>57.64339538784067</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P33" t="n">
-        <v>65.79225647093401</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q33" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10484,25 +10484,25 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>33.63624132272334</v>
+        <v>33.63624132272333</v>
       </c>
       <c r="K34" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L34" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M34" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N34" t="n">
-        <v>81.8777083996594</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O34" t="n">
-        <v>96.14558763217065</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P34" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q34" t="n">
         <v>65.34295837775146</v>
@@ -10563,28 +10563,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K35" t="n">
-        <v>135.2021224017645</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L35" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M35" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N35" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O35" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P35" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q35" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R35" t="n">
         <v>65.71641987298243</v>
@@ -10642,28 +10642,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J36" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K36" t="n">
-        <v>80.18462765360428</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L36" t="n">
-        <v>61.02768166666662</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M36" t="n">
-        <v>51.66403392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N36" t="n">
-        <v>38.4772403852201</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O36" t="n">
-        <v>57.64339538784067</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P36" t="n">
-        <v>65.79225647093401</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q36" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10724,22 +10724,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K37" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L37" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M37" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N37" t="n">
-        <v>81.8777083996594</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O37" t="n">
-        <v>96.14558763217065</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P37" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q37" t="n">
         <v>65.34295837775146</v>
@@ -10800,28 +10800,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K38" t="n">
-        <v>135.2021224017645</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L38" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M38" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N38" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O38" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P38" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q38" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R38" t="n">
         <v>65.71641987298243</v>
@@ -10879,28 +10879,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J39" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K39" t="n">
-        <v>80.18462765360428</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L39" t="n">
-        <v>61.02768166666662</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M39" t="n">
-        <v>51.66403392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N39" t="n">
-        <v>38.4772403852201</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O39" t="n">
-        <v>57.64339538784067</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P39" t="n">
-        <v>65.79225647093401</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q39" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -10961,22 +10961,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K40" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L40" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M40" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N40" t="n">
-        <v>81.8777083996594</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O40" t="n">
-        <v>96.14558763217065</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P40" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q40" t="n">
         <v>65.34295837775146</v>
@@ -11037,28 +11037,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K41" t="n">
-        <v>135.2021224017645</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L41" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M41" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N41" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O41" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P41" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q41" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R41" t="n">
         <v>65.71641987298243</v>
@@ -11116,28 +11116,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J42" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K42" t="n">
-        <v>80.18462765360428</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L42" t="n">
-        <v>61.02768166666662</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M42" t="n">
-        <v>51.66403392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N42" t="n">
-        <v>38.4772403852201</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O42" t="n">
-        <v>57.64339538784067</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P42" t="n">
-        <v>65.79225647093401</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q42" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11198,22 +11198,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K43" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L43" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M43" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N43" t="n">
-        <v>81.8777083996594</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O43" t="n">
-        <v>96.14558763217065</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P43" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q43" t="n">
         <v>65.34295837775146</v>
@@ -11274,28 +11274,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>124.4065376925154</v>
+        <v>124.5190384721106</v>
       </c>
       <c r="K44" t="n">
-        <v>135.2021224017645</v>
+        <v>135.370731907559</v>
       </c>
       <c r="L44" t="n">
-        <v>130.4556813016455</v>
+        <v>130.6648563030561</v>
       </c>
       <c r="M44" t="n">
-        <v>113.1677508152124</v>
+        <v>113.4004983079896</v>
       </c>
       <c r="N44" t="n">
-        <v>110.3385108327718</v>
+        <v>110.5750244233121</v>
       </c>
       <c r="O44" t="n">
-        <v>117.6594878035963</v>
+        <v>117.8828208804077</v>
       </c>
       <c r="P44" t="n">
-        <v>135.2691465090384</v>
+        <v>135.4597561231036</v>
       </c>
       <c r="Q44" t="n">
-        <v>150.2408356030927</v>
+        <v>150.3839754851235</v>
       </c>
       <c r="R44" t="n">
         <v>65.71641987298243</v>
@@ -11353,28 +11353,28 @@
         <v>10.12574714858493</v>
       </c>
       <c r="J45" t="n">
-        <v>93.10360779874216</v>
+        <v>93.17061249236157</v>
       </c>
       <c r="K45" t="n">
-        <v>80.18462765360428</v>
+        <v>80.29914934735042</v>
       </c>
       <c r="L45" t="n">
-        <v>61.02768166666662</v>
+        <v>61.18167021676314</v>
       </c>
       <c r="M45" t="n">
-        <v>51.66403392201833</v>
+        <v>51.84373129681028</v>
       </c>
       <c r="N45" t="n">
-        <v>38.4772403852201</v>
+        <v>38.66169381481656</v>
       </c>
       <c r="O45" t="n">
-        <v>57.64339538784067</v>
+        <v>57.81213424001893</v>
       </c>
       <c r="P45" t="n">
-        <v>65.79225647093401</v>
+        <v>65.92768427608706</v>
       </c>
       <c r="Q45" t="n">
-        <v>94.40381182187056</v>
+        <v>94.49434172313325</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -11435,22 +11435,22 @@
         <v>33.63624132272333</v>
       </c>
       <c r="K46" t="n">
-        <v>94.23489751479769</v>
+        <v>94.30397654773019</v>
       </c>
       <c r="L46" t="n">
-        <v>90.38034841238581</v>
+        <v>90.4687457914608</v>
       </c>
       <c r="M46" t="n">
-        <v>92.00221017711326</v>
+        <v>92.09541281912071</v>
       </c>
       <c r="N46" t="n">
-        <v>81.8777083996594</v>
+        <v>81.96869489115805</v>
       </c>
       <c r="O46" t="n">
-        <v>96.14558763217065</v>
+        <v>96.22962838366004</v>
       </c>
       <c r="P46" t="n">
-        <v>101.5236761802952</v>
+        <v>101.5955875616828</v>
       </c>
       <c r="Q46" t="n">
         <v>65.34295837775146</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>6.876045741711209</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G2" t="n">
-        <v>15.30273751513482</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22686,7 +22686,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>9.663381206337363e-13</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -22753,10 +22753,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.876045741711323</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G5" t="n">
-        <v>15.30273751513471</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22911,7 +22911,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -22923,7 +22923,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -22990,10 +22990,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>6.876045741711209</v>
+        <v>6.876045741711437</v>
       </c>
       <c r="G8" t="n">
-        <v>15.30273751513482</v>
+        <v>15.30273751513505</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23160,7 +23160,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23230,13 +23230,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H11" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I11" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,16 +23263,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S11" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T11" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U11" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V11" t="n">
         <v>327.7522584701349</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H12" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I12" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,16 +23342,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S12" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T12" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V12" t="n">
         <v>232.8005871494253</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H13" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I13" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J13" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23418,19 +23418,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R13" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S13" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T13" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U13" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V13" t="n">
         <v>252.137643323828</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H14" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I14" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,16 +23500,16 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S14" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T14" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U14" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,13 +23546,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H15" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I15" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23579,16 +23579,16 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S15" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T15" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V15" t="n">
         <v>232.8005871494253</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H16" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I16" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J16" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23655,19 +23655,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R16" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S16" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T16" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U16" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V16" t="n">
         <v>252.137643323828</v>
@@ -23704,13 +23704,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G17" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H17" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I17" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,16 +23737,16 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S17" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T17" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U17" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V17" t="n">
         <v>327.7522584701349</v>
@@ -23783,13 +23783,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H18" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I18" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S18" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T18" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23862,16 +23862,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H19" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I19" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J19" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23892,19 +23892,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R19" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S19" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T19" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23941,13 +23941,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>414.6394209322205</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H20" t="n">
-        <v>332.6816111609933</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I20" t="n">
-        <v>184.9033770075918</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,16 +23974,16 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>108.2020576396421</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S20" t="n">
-        <v>193.9047429530795</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T20" t="n">
-        <v>220.1921812224228</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U20" t="n">
-        <v>251.2925875812033</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V20" t="n">
         <v>327.7522584701349</v>
@@ -24020,13 +24020,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>136.9886115028333</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H21" t="n">
-        <v>108.8078027270625</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I21" t="n">
-        <v>77.17729322877356</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -24053,16 +24053,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>78.1225511337752</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S21" t="n">
-        <v>165.0909541227057</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T21" t="n">
-        <v>198.7342098268971</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9180330243711</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
@@ -24099,16 +24099,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G22" t="n">
-        <v>167.6934383748522</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H22" t="n">
-        <v>159.581762671374</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I22" t="n">
-        <v>146.5026060747993</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J22" t="n">
-        <v>72.32303257568917</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24129,19 +24129,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>61.24704325169439</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R22" t="n">
-        <v>163.9148667870056</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S22" t="n">
-        <v>218.8312701681198</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T22" t="n">
-        <v>226.6742779528716</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U22" t="n">
-        <v>286.3027998482942</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V22" t="n">
         <v>252.137643323828</v>
@@ -24178,13 +24178,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H23" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I23" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,16 +24211,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S23" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T23" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U23" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24257,13 +24257,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H24" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I24" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -24290,16 +24290,16 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S24" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T24" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U24" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V24" t="n">
         <v>232.8005871494253</v>
@@ -24336,16 +24336,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H25" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I25" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J25" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24366,19 +24366,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R25" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S25" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T25" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U25" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24415,13 +24415,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H26" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I26" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,16 +24448,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S26" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T26" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U26" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V26" t="n">
         <v>327.7522584701349</v>
@@ -24494,13 +24494,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H27" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I27" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,16 +24527,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S27" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T27" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V27" t="n">
         <v>232.8005871494253</v>
@@ -24573,16 +24573,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G28" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H28" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I28" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J28" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24603,19 +24603,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R28" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S28" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T28" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U28" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V28" t="n">
         <v>252.137643323828</v>
@@ -24652,13 +24652,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H29" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I29" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,16 +24685,16 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S29" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T29" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U29" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V29" t="n">
         <v>327.7522584701349</v>
@@ -24731,13 +24731,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H30" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I30" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,16 +24764,16 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S30" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T30" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
@@ -24810,16 +24810,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G31" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H31" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I31" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J31" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -24840,19 +24840,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R31" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S31" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T31" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24889,13 +24889,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H32" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I32" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,16 +24922,16 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S32" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T32" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U32" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24968,13 +24968,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H33" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I33" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S33" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T33" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25047,16 +25047,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G34" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H34" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I34" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J34" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -25077,19 +25077,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R34" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S34" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T34" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U34" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V34" t="n">
         <v>252.137643323828</v>
@@ -25126,13 +25126,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H35" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I35" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,16 +25159,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S35" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T35" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U35" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25205,13 +25205,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H36" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I36" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -25238,16 +25238,16 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S36" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T36" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
@@ -25284,16 +25284,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H37" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I37" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J37" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -25314,19 +25314,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R37" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S37" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T37" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U37" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V37" t="n">
         <v>252.137643323828</v>
@@ -25363,13 +25363,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H38" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I38" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,16 +25396,16 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S38" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T38" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U38" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V38" t="n">
         <v>327.7522584701349</v>
@@ -25442,13 +25442,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H39" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I39" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -25475,16 +25475,16 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S39" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T39" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
@@ -25521,16 +25521,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G40" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H40" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I40" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J40" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -25551,19 +25551,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R40" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S40" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T40" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25600,13 +25600,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H41" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I41" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,16 +25633,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S41" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T41" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U41" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25679,13 +25679,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H42" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I42" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25712,16 +25712,16 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S42" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T42" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
@@ -25758,16 +25758,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G43" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H43" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I43" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J43" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -25788,19 +25788,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R43" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S43" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T43" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V43" t="n">
         <v>252.137643323828</v>
@@ -25837,13 +25837,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>414.635400831718</v>
+        <v>414.6367263390697</v>
       </c>
       <c r="H44" t="n">
-        <v>332.6404403067219</v>
+        <v>332.654015158888</v>
       </c>
       <c r="I44" t="n">
-        <v>184.7483920829687</v>
+        <v>184.7994937051469</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25870,16 +25870,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>107.9495300014512</v>
+        <v>108.0327934026353</v>
       </c>
       <c r="S44" t="n">
-        <v>193.8131349128785</v>
+        <v>193.8433399116564</v>
       </c>
       <c r="T44" t="n">
-        <v>220.1745832324731</v>
+        <v>220.1803856409053</v>
       </c>
       <c r="U44" t="n">
-        <v>251.2922659731631</v>
+        <v>251.2923720137513</v>
       </c>
       <c r="V44" t="n">
         <v>327.7522584701349</v>
@@ -25916,13 +25916,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>136.9864605594371</v>
+        <v>136.9871697683942</v>
       </c>
       <c r="H45" t="n">
-        <v>108.7870291421568</v>
+        <v>108.7938786076111</v>
       </c>
       <c r="I45" t="n">
-        <v>77.10323662499998</v>
+        <v>77.12765456497084</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25949,16 +25949,16 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>77.98900396396388</v>
+        <v>78.03303713061706</v>
       </c>
       <c r="S45" t="n">
-        <v>165.0510012925171</v>
+        <v>165.0641745378389</v>
       </c>
       <c r="T45" t="n">
-        <v>198.7255400155763</v>
+        <v>198.728398625364</v>
       </c>
       <c r="U45" t="n">
-        <v>225.9178915149371</v>
+        <v>225.9179381734211</v>
       </c>
       <c r="V45" t="n">
         <v>232.8005871494253</v>
@@ -25995,16 +25995,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G46" t="n">
-        <v>167.6916350961637</v>
+        <v>167.6922296731294</v>
       </c>
       <c r="H46" t="n">
-        <v>159.5657298844887</v>
+        <v>159.571016214239</v>
       </c>
       <c r="I46" t="n">
-        <v>146.4483765666025</v>
+        <v>146.4662571175369</v>
       </c>
       <c r="J46" t="n">
-        <v>72.19554077241048</v>
+        <v>72.23757736389061</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -26025,19 +26025,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.09604325169438</v>
+        <v>61.14583096471014</v>
       </c>
       <c r="R46" t="n">
-        <v>163.8337848197924</v>
+        <v>163.8605191622716</v>
       </c>
       <c r="S46" t="n">
-        <v>218.7998439386116</v>
+        <v>218.8102057935515</v>
       </c>
       <c r="T46" t="n">
-        <v>226.6665730348389</v>
+        <v>226.6691135000563</v>
       </c>
       <c r="U46" t="n">
-        <v>286.3027014876384</v>
+        <v>286.3027339191093</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>333165.5208015452</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>333165.5208015452</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333165.5208015452</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>333165.5208015452</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>332944.9024887584</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>332944.9024887583</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>332944.902488761</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>332944.9024887608</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>332944.9024887584</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>332944.9024887584</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>332944.9024887584</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>332944.9024887584</v>
+        <v>333017.6447486461</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>491565.8032302234</v>
+        <v>491565.803230223</v>
       </c>
       <c r="C2" t="n">
-        <v>491565.8032302234</v>
+        <v>491565.803230223</v>
       </c>
       <c r="D2" t="n">
-        <v>491565.8032302234</v>
+        <v>491565.803230223</v>
       </c>
       <c r="E2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="F2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="G2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="H2" t="n">
-        <v>137157.3519974595</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="I2" t="n">
-        <v>137198.0898689349</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="J2" t="n">
-        <v>137198.0898689349</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="K2" t="n">
-        <v>137198.0898689379</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="L2" t="n">
-        <v>137198.0898689375</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="M2" t="n">
-        <v>137198.0898689349</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="N2" t="n">
-        <v>137198.0898689349</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="O2" t="n">
-        <v>137198.0898689349</v>
+        <v>137184.6577798363</v>
       </c>
       <c r="P2" t="n">
-        <v>137198.0898689349</v>
+        <v>137184.6577798363</v>
       </c>
     </row>
     <row r="3">
@@ -26322,7 +26322,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>132561.495</v>
+        <v>133100.0000000001</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26334,7 +26334,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>752.749</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>463150.73110211</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="C4" t="n">
-        <v>463150.7311021101</v>
+        <v>463844.333129713</v>
       </c>
       <c r="D4" t="n">
-        <v>463150.7311021101</v>
+        <v>463844.3331297129</v>
       </c>
       <c r="E4" t="n">
-        <v>70280.59613974771</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="F4" t="n">
-        <v>70280.59613974771</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="G4" t="n">
-        <v>70280.59613974771</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="H4" t="n">
-        <v>70280.59613974771</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="I4" t="n">
-        <v>69981.89690663294</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="J4" t="n">
-        <v>69981.89690663294</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="K4" t="n">
-        <v>69981.89690663564</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="L4" t="n">
-        <v>69981.89690663536</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="M4" t="n">
-        <v>69981.89690663294</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="N4" t="n">
-        <v>69981.89690663294</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="O4" t="n">
-        <v>69981.89690663294</v>
+        <v>70491.41612351945</v>
       </c>
       <c r="P4" t="n">
-        <v>69981.89690663294</v>
+        <v>70491.41612351945</v>
       </c>
     </row>
     <row r="5">
@@ -26426,40 +26426,40 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="F5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="G5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="H5" t="n">
-        <v>3597</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="I5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="J5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="K5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="L5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="M5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="N5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="O5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
       <c r="P5" t="n">
-        <v>3618.8</v>
+        <v>3611.612105008322</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-5212.527871886639</v>
+        <v>-5906.129899489948</v>
       </c>
       <c r="C6" t="n">
-        <v>-5212.527871886698</v>
+        <v>-5906.129899490006</v>
       </c>
       <c r="D6" t="n">
-        <v>-5212.527871886698</v>
+        <v>-5906.12989948989</v>
       </c>
       <c r="E6" t="n">
-        <v>-69281.73914228819</v>
+        <v>-70018.37044869152</v>
       </c>
       <c r="F6" t="n">
-        <v>63279.75585771177</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="G6" t="n">
-        <v>63279.75585771177</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="H6" t="n">
-        <v>63279.7558577118</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="I6" t="n">
-        <v>62844.64396230195</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="J6" t="n">
-        <v>63597.39296230194</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="K6" t="n">
-        <v>63597.39296230221</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="L6" t="n">
-        <v>63597.39296230217</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="M6" t="n">
-        <v>63597.39296230199</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="N6" t="n">
-        <v>63597.39296230199</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="O6" t="n">
-        <v>63597.39296230194</v>
+        <v>63081.62955130853</v>
       </c>
       <c r="P6" t="n">
-        <v>63597.39296230196</v>
+        <v>63081.62955130853</v>
       </c>
     </row>
   </sheetData>
@@ -26684,40 +26684,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="F3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="G3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="H3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="I3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="J3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="K3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="L3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="M3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="N3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="O3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="P3" t="n">
-        <v>166</v>
+        <v>165.6702800462533</v>
       </c>
     </row>
     <row r="4">
@@ -26892,7 +26892,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26901,28 +26901,28 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>165.6702800462533</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -26977,7 +26977,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -26986,7 +26986,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27301,22 +27301,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>382.7338416634812</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C2" t="n">
-        <v>365.2728917710079</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D2" t="n">
-        <v>354.6830416206833</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E2" t="n">
-        <v>381.9303700722621</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>339.4748021157671</v>
@@ -27361,16 +27361,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>327.7522584701355</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W2" t="n">
-        <v>349.2409687174135</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X2" t="n">
-        <v>369.7311006784694</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y2" t="n">
-        <v>386.2379386560539</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="3">
@@ -27380,16 +27380,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>166.5331836498674</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>172.7084989883158</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D3" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E3" t="n">
-        <v>157.645080455401</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F3" t="n">
         <v>145.0692123933839</v>
@@ -27440,16 +27440,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V3" t="n">
-        <v>232.8005871494254</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W3" t="n">
-        <v>251.6949831609197</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X3" t="n">
-        <v>205.7729852034776</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y3" t="n">
-        <v>205.6826957773045</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="4">
@@ -27459,10 +27459,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.8319801819374</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C4" t="n">
-        <v>167.2468210986279</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D4" t="n">
         <v>148.6154730182124</v>
@@ -27471,7 +27471,7 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F4" t="n">
-        <v>145.4210480229313</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G4" t="n">
         <v>167.9909793584588</v>
@@ -27519,16 +27519,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V4" t="n">
-        <v>252.1376433238281</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W4" t="n">
-        <v>286.5229983365911</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X4" t="n">
-        <v>225.7096553890362</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y4" t="n">
-        <v>218.584653352095</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="5">
@@ -27538,22 +27538,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382.7338416634813</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C5" t="n">
-        <v>365.2728917710081</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D5" t="n">
-        <v>354.6830416206834</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E5" t="n">
-        <v>381.9303700722625</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F5" t="n">
-        <v>400.0000000000001</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>400.0000000000003</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>339.4748021157671</v>
@@ -27598,16 +27598,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V5" t="n">
-        <v>327.7522584701353</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W5" t="n">
-        <v>349.2409687174135</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X5" t="n">
-        <v>369.7311006784695</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y5" t="n">
-        <v>386.2379386560543</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="6">
@@ -27617,19 +27617,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>166.5331836498676</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>172.708498988316</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4450655646389</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>157.6450804554011</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>145.069212393384</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
         <v>137.3435171632106</v>
@@ -27677,16 +27677,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
-        <v>232.8005871494256</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>251.6949831609199</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X6" t="n">
-        <v>205.7729852034778</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y6" t="n">
-        <v>205.6826957773047</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="7">
@@ -27696,19 +27696,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>179.8319801819375</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C7" t="n">
-        <v>167.246821098628</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D7" t="n">
-        <v>148.6154730182125</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E7" t="n">
-        <v>146.4339626465693</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F7" t="n">
-        <v>145.4210480229308</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
         <v>167.9909793584588</v>
@@ -27756,16 +27756,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V7" t="n">
-        <v>252.1376433238283</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W7" t="n">
-        <v>286.5229983365913</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X7" t="n">
-        <v>225.7096553890375</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y7" t="n">
-        <v>218.5846533520952</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="8">
@@ -27775,22 +27775,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>382.7338416634814</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>365.2728917710081</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
-        <v>354.6830416206835</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
-        <v>381.9303700722623</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400.0000000000002</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>339.4748021157671</v>
@@ -27835,16 +27835,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V8" t="n">
-        <v>327.7522584701353</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>349.2409687174136</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>369.7311006784695</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560543</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="9">
@@ -27854,19 +27854,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>166.5331836498676</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>172.708498988316</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646389</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
-        <v>157.6450804554012</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>145.069212393384</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G9" t="n">
         <v>137.3435171632106</v>
@@ -27914,16 +27914,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V9" t="n">
-        <v>232.8005871494256</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>251.6949831609198</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
-        <v>205.7729852034778</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y9" t="n">
-        <v>205.6826957773047</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="10">
@@ -27933,19 +27933,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179.8319801819375</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C10" t="n">
-        <v>167.246821098628</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D10" t="n">
-        <v>148.6154730182126</v>
+        <v>148.6154730182124</v>
       </c>
       <c r="E10" t="n">
-        <v>146.4339626465693</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F10" t="n">
-        <v>145.4210480229314</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
         <v>167.9909793584588</v>
@@ -27993,16 +27993,16 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V10" t="n">
-        <v>252.1376433238282</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W10" t="n">
-        <v>286.5229983365913</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X10" t="n">
-        <v>225.7096553890375</v>
+        <v>225.7096553890372</v>
       </c>
       <c r="Y10" t="n">
-        <v>218.5846533520952</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="11">
@@ -31670,49 +31670,49 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H11" t="n">
-        <v>6.793190954773867</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I11" t="n">
-        <v>25.57251256281407</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J11" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K11" t="n">
-        <v>84.37635678391959</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L11" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M11" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N11" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O11" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P11" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q11" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R11" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S11" t="n">
-        <v>15.11532663316584</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T11" t="n">
-        <v>2.903668341708543</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05306532663316579</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -31749,49 +31749,49 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H12" t="n">
-        <v>3.427641509433964</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I12" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J12" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K12" t="n">
-        <v>57.30948113207549</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L12" t="n">
-        <v>77.05966981132077</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M12" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N12" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O12" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P12" t="n">
-        <v>67.77141509433964</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q12" t="n">
-        <v>45.30339622641511</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R12" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S12" t="n">
-        <v>6.592216981132073</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T12" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -31828,49 +31828,49 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2975409836065574</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H13" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I13" t="n">
-        <v>8.94786885245902</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J13" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K13" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L13" t="n">
-        <v>44.23622950819674</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M13" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N13" t="n">
-        <v>45.53188524590168</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O13" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P13" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R13" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S13" t="n">
-        <v>5.185327868852458</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T13" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -31907,49 +31907,49 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H14" t="n">
-        <v>6.793190954773867</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I14" t="n">
-        <v>25.57251256281407</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J14" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K14" t="n">
-        <v>84.37635678391959</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L14" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M14" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N14" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O14" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P14" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q14" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R14" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S14" t="n">
-        <v>15.11532663316584</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T14" t="n">
-        <v>2.903668341708543</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U14" t="n">
-        <v>0.05306532663316579</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -31986,49 +31986,49 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H15" t="n">
-        <v>3.427641509433964</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I15" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J15" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K15" t="n">
-        <v>57.30948113207549</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L15" t="n">
-        <v>77.05966981132077</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M15" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N15" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O15" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P15" t="n">
-        <v>67.77141509433964</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q15" t="n">
-        <v>45.30339622641511</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R15" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S15" t="n">
-        <v>6.592216981132073</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T15" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -32065,49 +32065,49 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2975409836065574</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H16" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I16" t="n">
-        <v>8.94786885245902</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J16" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K16" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L16" t="n">
-        <v>44.23622950819674</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M16" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N16" t="n">
-        <v>45.53188524590168</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O16" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P16" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q16" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R16" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S16" t="n">
-        <v>5.185327868852458</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T16" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -32144,49 +32144,49 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H17" t="n">
-        <v>6.793190954773867</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I17" t="n">
-        <v>25.57251256281407</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J17" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K17" t="n">
-        <v>84.37635678391959</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L17" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M17" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N17" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O17" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P17" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q17" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R17" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S17" t="n">
-        <v>15.11532663316584</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T17" t="n">
-        <v>2.903668341708543</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U17" t="n">
-        <v>0.05306532663316579</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -32223,49 +32223,49 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H18" t="n">
-        <v>3.427641509433964</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I18" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J18" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K18" t="n">
-        <v>57.30948113207549</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L18" t="n">
-        <v>77.05966981132077</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M18" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N18" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O18" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P18" t="n">
-        <v>67.77141509433964</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q18" t="n">
-        <v>45.30339622641511</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R18" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S18" t="n">
-        <v>6.592216981132073</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T18" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -32302,49 +32302,49 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2975409836065574</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H19" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I19" t="n">
-        <v>8.94786885245902</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J19" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K19" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L19" t="n">
-        <v>44.23622950819674</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M19" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N19" t="n">
-        <v>45.53188524590168</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O19" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P19" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q19" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R19" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S19" t="n">
-        <v>5.185327868852458</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T19" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -32381,49 +32381,49 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6633165829145724</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H20" t="n">
-        <v>6.793190954773867</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I20" t="n">
-        <v>25.57251256281407</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J20" t="n">
-        <v>56.29816582914574</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K20" t="n">
-        <v>84.37635678391959</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L20" t="n">
-        <v>104.6763316582914</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M20" t="n">
-        <v>116.4725879396985</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N20" t="n">
-        <v>118.3572361809045</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O20" t="n">
-        <v>111.7613819095477</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P20" t="n">
-        <v>95.38575376884421</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q20" t="n">
-        <v>71.63072864321607</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R20" t="n">
-        <v>41.66706030150754</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S20" t="n">
-        <v>15.11532663316584</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T20" t="n">
-        <v>2.903668341708543</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U20" t="n">
-        <v>0.05306532663316579</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -32460,49 +32460,49 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3549056603773585</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H21" t="n">
-        <v>3.427641509433964</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I21" t="n">
-        <v>12.21933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J21" t="n">
-        <v>33.53080188679246</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K21" t="n">
-        <v>57.30948113207549</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L21" t="n">
-        <v>77.05966981132077</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M21" t="n">
-        <v>89.925</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N21" t="n">
-        <v>92.30504716981133</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O21" t="n">
-        <v>84.44108490566039</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P21" t="n">
-        <v>67.77141509433964</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q21" t="n">
-        <v>45.30339622641511</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R21" t="n">
-        <v>22.03528301886793</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S21" t="n">
-        <v>6.592216981132073</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T21" t="n">
-        <v>1.430518867924528</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0233490566037736</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -32539,49 +32539,49 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2975409836065574</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H22" t="n">
-        <v>2.645409836065576</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I22" t="n">
-        <v>8.94786885245902</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J22" t="n">
-        <v>21.03614754098361</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K22" t="n">
-        <v>34.56885245901638</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L22" t="n">
-        <v>44.23622950819674</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M22" t="n">
-        <v>46.64090163934426</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N22" t="n">
-        <v>45.53188524590168</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O22" t="n">
-        <v>42.05606557377051</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P22" t="n">
-        <v>35.9862295081967</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q22" t="n">
-        <v>24.915</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R22" t="n">
-        <v>13.37852459016393</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S22" t="n">
-        <v>5.185327868852458</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T22" t="n">
-        <v>1.271311475409836</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U22" t="n">
-        <v>0.01622950819672133</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -32618,49 +32618,49 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H23" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I23" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J23" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K23" t="n">
-        <v>84.88772864321608</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L23" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M23" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N23" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O23" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P23" t="n">
-        <v>95.96384924623115</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q23" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R23" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S23" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T23" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U23" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -32697,49 +32697,49 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H24" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I24" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J24" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K24" t="n">
-        <v>57.65681132075472</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L24" t="n">
-        <v>77.52669811320756</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M24" t="n">
-        <v>90.46999999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N24" t="n">
-        <v>92.86447169811321</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O24" t="n">
-        <v>84.95284905660377</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P24" t="n">
-        <v>68.18215094339624</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q24" t="n">
-        <v>45.57796226415095</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R24" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S24" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T24" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U24" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -32776,49 +32776,49 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H25" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I25" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J25" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K25" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L25" t="n">
-        <v>44.50432786885246</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M25" t="n">
-        <v>46.92357377049179</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N25" t="n">
-        <v>45.8078360655738</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O25" t="n">
-        <v>42.31095081967214</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P25" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q25" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R25" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S25" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T25" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -32855,49 +32855,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H26" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I26" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J26" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K26" t="n">
-        <v>84.88772864321611</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L26" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M26" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N26" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O26" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P26" t="n">
-        <v>95.96384924623116</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q26" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R26" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S26" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T26" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U26" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -32934,49 +32934,49 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H27" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I27" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J27" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K27" t="n">
-        <v>57.65681132075474</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L27" t="n">
-        <v>77.52669811320757</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M27" t="n">
-        <v>90.47000000000001</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N27" t="n">
-        <v>92.86447169811323</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O27" t="n">
-        <v>84.9528490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P27" t="n">
-        <v>68.18215094339625</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q27" t="n">
-        <v>45.57796226415096</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R27" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S27" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T27" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U27" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -33013,49 +33013,49 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H28" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I28" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J28" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K28" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L28" t="n">
-        <v>44.50432786885248</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M28" t="n">
-        <v>46.92357377049181</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N28" t="n">
-        <v>45.80783606557381</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O28" t="n">
-        <v>42.31095081967216</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P28" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q28" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R28" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S28" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T28" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U28" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -33092,49 +33092,49 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H29" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I29" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J29" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K29" t="n">
-        <v>84.88772864321611</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L29" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M29" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N29" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O29" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P29" t="n">
-        <v>95.96384924623116</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q29" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R29" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S29" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T29" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U29" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -33171,49 +33171,49 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H30" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I30" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J30" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K30" t="n">
-        <v>57.65681132075474</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L30" t="n">
-        <v>77.52669811320757</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M30" t="n">
-        <v>90.47000000000001</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N30" t="n">
-        <v>92.86447169811323</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O30" t="n">
-        <v>84.9528490566038</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P30" t="n">
-        <v>68.18215094339625</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q30" t="n">
-        <v>45.57796226415096</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R30" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S30" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T30" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U30" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -33250,49 +33250,49 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H31" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I31" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J31" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K31" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L31" t="n">
-        <v>44.50432786885248</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M31" t="n">
-        <v>46.92357377049181</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N31" t="n">
-        <v>45.80783606557381</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O31" t="n">
-        <v>42.31095081967216</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P31" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q31" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R31" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S31" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T31" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -33329,49 +33329,49 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H32" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I32" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J32" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K32" t="n">
-        <v>84.88772864321608</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L32" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M32" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N32" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O32" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P32" t="n">
-        <v>95.96384924623115</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q32" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R32" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S32" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T32" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U32" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -33408,49 +33408,49 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H33" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I33" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J33" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K33" t="n">
-        <v>57.65681132075472</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L33" t="n">
-        <v>77.52669811320756</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M33" t="n">
-        <v>90.46999999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N33" t="n">
-        <v>92.86447169811321</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O33" t="n">
-        <v>84.95284905660377</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P33" t="n">
-        <v>68.18215094339624</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q33" t="n">
-        <v>45.57796226415095</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R33" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S33" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T33" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U33" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -33487,49 +33487,49 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H34" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I34" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J34" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K34" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L34" t="n">
-        <v>44.50432786885246</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M34" t="n">
-        <v>46.92357377049179</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N34" t="n">
-        <v>45.8078360655738</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O34" t="n">
-        <v>42.31095081967214</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P34" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q34" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R34" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S34" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T34" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U34" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -33566,49 +33566,49 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H35" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I35" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J35" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K35" t="n">
-        <v>84.88772864321608</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L35" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M35" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N35" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O35" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P35" t="n">
-        <v>95.96384924623115</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q35" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R35" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S35" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T35" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U35" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -33645,49 +33645,49 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H36" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I36" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J36" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K36" t="n">
-        <v>57.65681132075472</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L36" t="n">
-        <v>77.52669811320756</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M36" t="n">
-        <v>90.46999999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N36" t="n">
-        <v>92.86447169811321</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O36" t="n">
-        <v>84.95284905660377</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P36" t="n">
-        <v>68.18215094339624</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q36" t="n">
-        <v>45.57796226415095</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R36" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S36" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T36" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U36" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -33724,49 +33724,49 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H37" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I37" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J37" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K37" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L37" t="n">
-        <v>44.50432786885246</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M37" t="n">
-        <v>46.92357377049179</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N37" t="n">
-        <v>45.8078360655738</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O37" t="n">
-        <v>42.31095081967214</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P37" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q37" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R37" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S37" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T37" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U37" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -33803,49 +33803,49 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H38" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I38" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J38" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K38" t="n">
-        <v>84.88772864321608</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L38" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M38" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N38" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O38" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P38" t="n">
-        <v>95.96384924623115</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q38" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R38" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S38" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T38" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U38" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -33882,49 +33882,49 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H39" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I39" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J39" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K39" t="n">
-        <v>57.65681132075472</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L39" t="n">
-        <v>77.52669811320756</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M39" t="n">
-        <v>90.46999999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N39" t="n">
-        <v>92.86447169811321</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O39" t="n">
-        <v>84.95284905660377</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P39" t="n">
-        <v>68.18215094339624</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q39" t="n">
-        <v>45.57796226415095</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R39" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S39" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T39" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U39" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -33961,49 +33961,49 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H40" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I40" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J40" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K40" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L40" t="n">
-        <v>44.50432786885246</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M40" t="n">
-        <v>46.92357377049179</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N40" t="n">
-        <v>45.8078360655738</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O40" t="n">
-        <v>42.31095081967214</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P40" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q40" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R40" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S40" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T40" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U40" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -34040,49 +34040,49 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H41" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I41" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J41" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K41" t="n">
-        <v>84.88772864321608</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L41" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M41" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N41" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O41" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P41" t="n">
-        <v>95.96384924623115</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q41" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R41" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S41" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T41" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U41" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -34119,49 +34119,49 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H42" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I42" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J42" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K42" t="n">
-        <v>57.65681132075472</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L42" t="n">
-        <v>77.52669811320756</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M42" t="n">
-        <v>90.46999999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N42" t="n">
-        <v>92.86447169811321</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O42" t="n">
-        <v>84.95284905660377</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P42" t="n">
-        <v>68.18215094339624</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q42" t="n">
-        <v>45.57796226415095</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R42" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S42" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T42" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U42" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -34198,49 +34198,49 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H43" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I43" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J43" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K43" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L43" t="n">
-        <v>44.50432786885246</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M43" t="n">
-        <v>46.92357377049179</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N43" t="n">
-        <v>45.8078360655738</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O43" t="n">
-        <v>42.31095081967214</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P43" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q43" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R43" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S43" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T43" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U43" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -34277,49 +34277,49 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.667336683417085</v>
+        <v>0.6660111760653394</v>
       </c>
       <c r="H44" t="n">
-        <v>6.834361809045222</v>
+        <v>6.820786956879159</v>
       </c>
       <c r="I44" t="n">
-        <v>25.72749748743719</v>
+        <v>25.67639586525902</v>
       </c>
       <c r="J44" t="n">
-        <v>56.63936683417086</v>
+        <v>56.52686605457566</v>
       </c>
       <c r="K44" t="n">
-        <v>84.88772864321608</v>
+        <v>84.71911913742149</v>
       </c>
       <c r="L44" t="n">
-        <v>105.3107336683417</v>
+        <v>105.1015586669311</v>
       </c>
       <c r="M44" t="n">
-        <v>117.1784824120603</v>
+        <v>116.9457349192831</v>
       </c>
       <c r="N44" t="n">
-        <v>119.0745527638191</v>
+        <v>118.8380391732788</v>
       </c>
       <c r="O44" t="n">
-        <v>112.4387236180904</v>
+        <v>112.215390541279</v>
       </c>
       <c r="P44" t="n">
-        <v>95.96384924623115</v>
+        <v>95.77323963216597</v>
       </c>
       <c r="Q44" t="n">
-        <v>72.06485427135678</v>
+        <v>71.92171438932597</v>
       </c>
       <c r="R44" t="n">
-        <v>41.91958793969849</v>
+        <v>41.83632453851442</v>
       </c>
       <c r="S44" t="n">
-        <v>15.20693467336684</v>
+        <v>15.17672967458894</v>
       </c>
       <c r="T44" t="n">
-        <v>2.921266331658291</v>
+        <v>2.915463923226025</v>
       </c>
       <c r="U44" t="n">
-        <v>0.05338693467336678</v>
+        <v>0.05328089408522715</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -34356,49 +34356,49 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3570566037735849</v>
+        <v>0.3563473948164694</v>
       </c>
       <c r="H45" t="n">
-        <v>3.448415094339623</v>
+        <v>3.441565628885376</v>
       </c>
       <c r="I45" t="n">
-        <v>12.2933962264151</v>
+        <v>12.26897828644423</v>
       </c>
       <c r="J45" t="n">
-        <v>33.73401886792453</v>
+        <v>33.66701417430512</v>
       </c>
       <c r="K45" t="n">
-        <v>57.65681132075472</v>
+        <v>57.54228962700857</v>
       </c>
       <c r="L45" t="n">
-        <v>77.52669811320756</v>
+        <v>77.37270956311104</v>
       </c>
       <c r="M45" t="n">
-        <v>90.46999999999998</v>
+        <v>90.29030262520804</v>
       </c>
       <c r="N45" t="n">
-        <v>92.86447169811321</v>
+        <v>92.68001826851675</v>
       </c>
       <c r="O45" t="n">
-        <v>84.95284905660377</v>
+        <v>84.7841102044255</v>
       </c>
       <c r="P45" t="n">
-        <v>68.18215094339624</v>
+        <v>68.04672313824318</v>
       </c>
       <c r="Q45" t="n">
-        <v>45.57796226415095</v>
+        <v>45.48743236288827</v>
       </c>
       <c r="R45" t="n">
-        <v>22.16883018867926</v>
+        <v>22.12479702202607</v>
       </c>
       <c r="S45" t="n">
-        <v>6.63216981132075</v>
+        <v>6.61899656599889</v>
       </c>
       <c r="T45" t="n">
-        <v>1.439188679245283</v>
+        <v>1.436330069457611</v>
       </c>
       <c r="U45" t="n">
-        <v>0.02349056603773586</v>
+        <v>0.0234439075537151</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -34435,49 +34435,49 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2993442622950819</v>
+        <v>0.2987496853293092</v>
       </c>
       <c r="H46" t="n">
-        <v>2.661442622950821</v>
+        <v>2.656156293200588</v>
       </c>
       <c r="I46" t="n">
-        <v>9.00209836065574</v>
+        <v>8.984217809721411</v>
       </c>
       <c r="J46" t="n">
-        <v>21.16363934426229</v>
+        <v>21.12160275278216</v>
       </c>
       <c r="K46" t="n">
-        <v>34.77836065573769</v>
+        <v>34.70928162280519</v>
       </c>
       <c r="L46" t="n">
-        <v>44.50432786885246</v>
+        <v>44.41593048977749</v>
       </c>
       <c r="M46" t="n">
-        <v>46.92357377049179</v>
+        <v>46.83037112848434</v>
       </c>
       <c r="N46" t="n">
-        <v>45.8078360655738</v>
+        <v>45.71684957407514</v>
       </c>
       <c r="O46" t="n">
-        <v>42.31095081967214</v>
+        <v>42.22691006818274</v>
       </c>
       <c r="P46" t="n">
-        <v>36.20432786885244</v>
+        <v>36.1324164874648</v>
       </c>
       <c r="Q46" t="n">
-        <v>25.066</v>
+        <v>25.01621228698425</v>
       </c>
       <c r="R46" t="n">
-        <v>13.45960655737704</v>
+        <v>13.43287221489784</v>
       </c>
       <c r="S46" t="n">
-        <v>5.216754098360654</v>
+        <v>5.206392243420778</v>
       </c>
       <c r="T46" t="n">
-        <v>1.279016393442622</v>
+        <v>1.27647592822523</v>
       </c>
       <c r="U46" t="n">
-        <v>0.01632786885245903</v>
+        <v>0.0162954373815987</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
